--- a/diseases/d042/2010-2014.xlsx
+++ b/diseases/d042/2010-2014.xlsx
@@ -1357,9 +1357,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1753,9 +1750,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2741,9 +2735,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3729,9 +3720,6 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -4717,9 +4705,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5705,9 +5690,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6693,9 +6675,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7681,9 +7660,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -8669,9 +8645,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -9657,9 +9630,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -10645,9 +10615,6 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
@@ -11633,9 +11600,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -12621,9 +12585,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -13609,9 +13570,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -14005,9 +13963,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -14153,9 +14108,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -15141,9 +15093,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -15289,9 +15238,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -16277,9 +16223,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -16425,9 +16368,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -17413,9 +17353,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -17561,9 +17498,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -18549,9 +18483,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -18697,9 +18628,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -19685,9 +19613,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -19833,9 +19758,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -20821,9 +20743,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -20969,9 +20888,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -21957,9 +21873,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -22105,9 +22018,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -23093,9 +23003,6 @@
       <c r="O138" t="n">
         <v>1</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -23241,9 +23148,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -24229,9 +24133,6 @@
       <c r="O145" t="n">
         <v>2</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.004071027750394744</v>
       </c>
@@ -24377,9 +24278,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -25365,9 +25263,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -25513,9 +25408,6 @@
       <c r="O153" t="n">
         <v>1</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -26501,9 +26393,6 @@
       <c r="O159" t="n">
         <v>4</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.008142055500789488</v>
       </c>
@@ -26649,9 +26538,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -27637,9 +27523,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -28033,9 +27916,6 @@
       <c r="O168" t="n">
         <v>1</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -28773,9 +28653,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -29513,9 +29390,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -30253,9 +30127,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -30993,9 +30864,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -31733,9 +31601,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -32473,9 +32338,6 @@
       <c r="O198" t="n">
         <v>1</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -33213,9 +33075,6 @@
       <c r="O203" t="n">
         <v>1</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -33953,9 +33812,6 @@
       <c r="O208" t="n">
         <v>1</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -34693,9 +34549,6 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -35433,9 +35286,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -36173,9 +36023,6 @@
       <c r="O223" t="n">
         <v>1</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -36913,9 +36760,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -37309,9 +37153,6 @@
       <c r="O230" t="n">
         <v>1</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -37457,9 +37298,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -38445,9 +38283,6 @@
       <c r="O237" t="n">
         <v>0</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0</v>
       </c>
@@ -38593,9 +38428,6 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
@@ -39581,9 +39413,6 @@
       <c r="O244" t="n">
         <v>1</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -39729,9 +39558,6 @@
       <c r="O245" t="n">
         <v>1</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -40717,9 +40543,6 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0</v>
       </c>
@@ -40865,9 +40688,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0</v>
       </c>
@@ -41853,9 +41673,6 @@
       <c r="O258" t="n">
         <v>2</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -42001,9 +41818,6 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -42989,9 +42803,6 @@
       <c r="O265" t="n">
         <v>2</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -43137,9 +42948,6 @@
       <c r="O266" t="n">
         <v>0</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0</v>
       </c>
@@ -44125,9 +43933,6 @@
       <c r="O272" t="n">
         <v>0</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0</v>
       </c>
@@ -44273,9 +44078,6 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -45261,9 +45063,6 @@
       <c r="O279" t="n">
         <v>0</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0</v>
       </c>
@@ -45409,9 +45208,6 @@
       <c r="O280" t="n">
         <v>0</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0</v>
       </c>
@@ -46397,9 +46193,6 @@
       <c r="O286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
@@ -46545,9 +46338,6 @@
       <c r="O287" t="n">
         <v>0</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0</v>
       </c>
@@ -47533,9 +47323,6 @@
       <c r="O293" t="n">
         <v>0</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0</v>
       </c>
@@ -47681,9 +47468,6 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0</v>
       </c>
@@ -48669,9 +48453,6 @@
       <c r="O300" t="n">
         <v>0</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0</v>
       </c>
@@ -48817,9 +48598,6 @@
       <c r="O301" t="n">
         <v>0</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0</v>
       </c>
@@ -49805,9 +49583,6 @@
       <c r="O307" t="n">
         <v>1</v>
       </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
       <c r="R307" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -49953,9 +49728,6 @@
       <c r="O308" t="n">
         <v>0</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0</v>
       </c>
@@ -50941,9 +50713,6 @@
       <c r="O314" t="n">
         <v>0</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>0</v>
       </c>
@@ -51337,9 +51106,6 @@
       <c r="O316" t="n">
         <v>0</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>0</v>
       </c>
@@ -52077,9 +51843,6 @@
       <c r="O321" t="n">
         <v>0</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0</v>
       </c>
@@ -52817,9 +52580,6 @@
       <c r="O326" t="n">
         <v>0</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0</v>
       </c>
@@ -53557,9 +53317,6 @@
       <c r="O331" t="n">
         <v>0</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0</v>
       </c>
@@ -54297,9 +54054,6 @@
       <c r="O336" t="n">
         <v>1</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -55037,9 +54791,6 @@
       <c r="O341" t="n">
         <v>1</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -55777,9 +55528,6 @@
       <c r="O346" t="n">
         <v>1</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -56517,9 +56265,6 @@
       <c r="O351" t="n">
         <v>1</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -57257,9 +57002,6 @@
       <c r="O356" t="n">
         <v>0</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>0</v>
       </c>
@@ -57997,9 +57739,6 @@
       <c r="O361" t="n">
         <v>0</v>
       </c>
-      <c r="Q361" t="n">
-        <v>0</v>
-      </c>
       <c r="R361" t="n">
         <v>0</v>
       </c>
@@ -58737,9 +58476,6 @@
       <c r="O366" t="n">
         <v>2</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0.003957335530340491</v>
       </c>
@@ -59475,9 +59211,6 @@
         <v>0</v>
       </c>
       <c r="O371" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q371" t="n">
         <v>0</v>
       </c>
       <c r="R371" t="n">
